--- a/Grupos.xlsx
+++ b/Grupos.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC-DOCENTE\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC-DOCENTE\Documents\Trabajo-Colaborativo\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15360" windowHeight="7650"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="7470" windowHeight="7215"/>
   </bookViews>
   <sheets>
     <sheet name="Lista alumnos" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="158">
   <si>
     <t>UNIVERSIDAD NACIONAL AGRARIA LA MOLINA</t>
   </si>
@@ -599,19 +599,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -622,6 +609,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -909,8 +909,8 @@
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
     <col min="3" max="3" width="33.42578125" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" style="11" customWidth="1"/>
-    <col min="5" max="5" width="21.42578125" style="11" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="21.42578125" style="6" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
     <col min="7" max="8" width="20" customWidth="1"/>
     <col min="9" max="9" width="50" customWidth="1"/>
@@ -918,143 +918,143 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
+      <c r="A2" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
@@ -1066,10 +1066,10 @@
       <c r="C11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="7">
         <v>46164</v>
       </c>
-      <c r="E11" s="12"/>
+      <c r="E11" s="7"/>
       <c r="F11" s="1" t="s">
         <v>18</v>
       </c>
@@ -1096,13 +1096,13 @@
       <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="10">
-        <v>1</v>
-      </c>
-      <c r="E12" s="10" t="s">
+      <c r="D12" s="5">
+        <v>1</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>152</v>
       </c>
       <c r="F12" s="3" t="s">
@@ -1134,10 +1134,10 @@
       <c r="C13" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D13" s="10">
-        <v>1</v>
-      </c>
-      <c r="E13" s="10" t="s">
+      <c r="D13" s="5">
+        <v>1</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>152</v>
       </c>
       <c r="F13" s="3" t="s">
@@ -1169,10 +1169,10 @@
       <c r="C14" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="5">
         <v>0</v>
       </c>
-      <c r="E14" s="10"/>
+      <c r="E14" s="5"/>
       <c r="F14" s="3" t="s">
         <v>38</v>
       </c>
@@ -1202,10 +1202,10 @@
       <c r="C15" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D15" s="10">
-        <v>1</v>
-      </c>
-      <c r="E15" s="10" t="s">
+      <c r="D15" s="5">
+        <v>1</v>
+      </c>
+      <c r="E15" s="5" t="s">
         <v>152</v>
       </c>
       <c r="F15" s="3" t="s">
@@ -1237,10 +1237,10 @@
       <c r="C16" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D16" s="10">
-        <v>1</v>
-      </c>
-      <c r="E16" s="10" t="s">
+      <c r="D16" s="5">
+        <v>1</v>
+      </c>
+      <c r="E16" s="5" t="s">
         <v>152</v>
       </c>
       <c r="F16" s="3" t="s">
@@ -1264,25 +1264,25 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D17" s="10">
-        <v>1</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>153</v>
+        <v>45</v>
+      </c>
+      <c r="D17" s="5">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>156</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>28</v>
@@ -1307,10 +1307,10 @@
       <c r="C18" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="5">
         <v>0</v>
       </c>
-      <c r="E18" s="10"/>
+      <c r="E18" s="5"/>
       <c r="F18" s="3" t="s">
         <v>54</v>
       </c>
@@ -1332,25 +1332,25 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D19" s="10">
-        <v>1</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>153</v>
+        <v>116</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="D19" s="5">
+        <v>1</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>156</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>50</v>
+        <v>118</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>51</v>
+        <v>119</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>28</v>
@@ -1367,58 +1367,60 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>84</v>
+        <v>148</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D20" s="10">
-        <v>1</v>
-      </c>
-      <c r="E20" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="D20" s="5">
+        <v>1</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>2</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" s="5">
+        <v>1</v>
+      </c>
+      <c r="E21" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
-        <v>10</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D21" s="10">
-        <v>0</v>
-      </c>
-      <c r="E21" s="10"/>
       <c r="F21" s="3" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>28</v>
@@ -1435,25 +1437,25 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D22" s="10">
-        <v>1</v>
-      </c>
-      <c r="E22" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" s="5">
+        <v>1</v>
+      </c>
+      <c r="E22" s="5" t="s">
         <v>153</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>94</v>
+        <v>50</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>28</v>
@@ -1470,25 +1472,25 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>140</v>
+        <v>84</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D23" s="10">
-        <v>1</v>
-      </c>
-      <c r="E23" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="D23" s="5">
+        <v>1</v>
+      </c>
+      <c r="E23" s="5" t="s">
         <v>153</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>142</v>
+        <v>86</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>143</v>
+        <v>87</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>28</v>
@@ -1505,25 +1507,25 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D24" s="10">
-        <v>1</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>155</v>
+        <v>93</v>
+      </c>
+      <c r="D24" s="5">
+        <v>1</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>153</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>28</v>
@@ -1540,25 +1542,25 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>68</v>
+        <v>140</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D25" s="10">
-        <v>1</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>155</v>
+        <v>141</v>
+      </c>
+      <c r="D25" s="5">
+        <v>1</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>153</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>70</v>
+        <v>142</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>28</v>
@@ -1575,25 +1577,25 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D26" s="10">
-        <v>1</v>
-      </c>
-      <c r="E26" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26" s="5">
+        <v>1</v>
+      </c>
+      <c r="E26" s="5" t="s">
         <v>155</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>28</v>
@@ -1610,25 +1612,25 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D27" s="10">
-        <v>1</v>
-      </c>
-      <c r="E27" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D27" s="5">
+        <v>1</v>
+      </c>
+      <c r="E27" s="5" t="s">
         <v>155</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>111</v>
+        <v>71</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>28</v>
@@ -1645,25 +1647,25 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>128</v>
+        <v>80</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D28" s="10">
-        <v>1</v>
-      </c>
-      <c r="E28" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D28" s="5">
+        <v>1</v>
+      </c>
+      <c r="E28" s="5" t="s">
         <v>155</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>130</v>
+        <v>82</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>131</v>
+        <v>83</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>28</v>
@@ -1680,25 +1682,25 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D29" s="10">
-        <v>1</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>156</v>
+        <v>109</v>
+      </c>
+      <c r="D29" s="5">
+        <v>1</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>155</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>47</v>
+        <v>111</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>28</v>
@@ -1715,25 +1717,25 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D30" s="10">
-        <v>1</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>156</v>
+        <v>128</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="D30" s="5">
+        <v>1</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>155</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>28</v>
@@ -1750,25 +1752,25 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>148</v>
+        <v>64</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="D31" s="10">
-        <v>1</v>
-      </c>
-      <c r="E31" s="10" t="s">
-        <v>156</v>
+        <v>65</v>
+      </c>
+      <c r="D31" s="5">
+        <v>1</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>154</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>150</v>
+        <v>66</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>151</v>
+        <v>67</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>28</v>
@@ -1793,10 +1795,10 @@
       <c r="C32" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D32" s="10">
-        <v>1</v>
-      </c>
-      <c r="E32" s="10" t="s">
+      <c r="D32" s="5">
+        <v>1</v>
+      </c>
+      <c r="E32" s="5" t="s">
         <v>154</v>
       </c>
       <c r="F32" s="3" t="s">
@@ -1825,13 +1827,13 @@
       <c r="B33" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="D33" s="10">
-        <v>1</v>
-      </c>
-      <c r="E33" s="10" t="s">
+      <c r="D33" s="5">
+        <v>1</v>
+      </c>
+      <c r="E33" s="5" t="s">
         <v>154</v>
       </c>
       <c r="F33" s="3" t="s">
@@ -1863,10 +1865,10 @@
       <c r="C34" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D34" s="10">
-        <v>1</v>
-      </c>
-      <c r="E34" s="10" t="s">
+      <c r="D34" s="5">
+        <v>1</v>
+      </c>
+      <c r="E34" s="5" t="s">
         <v>154</v>
       </c>
       <c r="F34" s="3" t="s">
@@ -1898,10 +1900,10 @@
       <c r="C35" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D35" s="10">
-        <v>1</v>
-      </c>
-      <c r="E35" s="10" t="s">
+      <c r="D35" s="5">
+        <v>1</v>
+      </c>
+      <c r="E35" s="5" t="s">
         <v>154</v>
       </c>
       <c r="F35" s="3" t="s">
@@ -1933,10 +1935,10 @@
       <c r="C36" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D36" s="10">
-        <v>1</v>
-      </c>
-      <c r="E36" s="10" t="s">
+      <c r="D36" s="5">
+        <v>1</v>
+      </c>
+      <c r="E36" s="5" t="s">
         <v>154</v>
       </c>
       <c r="F36" s="3" t="s">
@@ -1968,10 +1970,10 @@
       <c r="C37" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D37" s="10">
-        <v>1</v>
-      </c>
-      <c r="E37" s="10" t="s">
+      <c r="D37" s="5">
+        <v>1</v>
+      </c>
+      <c r="E37" s="5" t="s">
         <v>157</v>
       </c>
       <c r="F37" s="3" t="s">
@@ -2003,10 +2005,10 @@
       <c r="C38" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="D38" s="10">
+      <c r="D38" s="5">
         <v>0</v>
       </c>
-      <c r="E38" s="10"/>
+      <c r="E38" s="5"/>
       <c r="F38" s="3" t="s">
         <v>134</v>
       </c>
@@ -2036,10 +2038,10 @@
       <c r="C39" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="D39" s="10">
+      <c r="D39" s="5">
         <v>0</v>
       </c>
-      <c r="E39" s="10"/>
+      <c r="E39" s="5"/>
       <c r="F39" s="3" t="s">
         <v>138</v>
       </c>
@@ -2066,13 +2068,13 @@
       <c r="B40" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C40" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="D40" s="10">
-        <v>1</v>
-      </c>
-      <c r="E40" s="10" t="s">
+      <c r="D40" s="5">
+        <v>1</v>
+      </c>
+      <c r="E40" s="5" t="s">
         <v>157</v>
       </c>
       <c r="F40" s="3" t="s">
@@ -2104,10 +2106,10 @@
       <c r="C41" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D41" s="10">
+      <c r="D41" s="5">
         <v>0</v>
       </c>
-      <c r="E41" s="10"/>
+      <c r="E41" s="5"/>
       <c r="F41" s="3" t="s">
         <v>146</v>
       </c>
@@ -2137,10 +2139,10 @@
       <c r="C42" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D42" s="10">
-        <v>1</v>
-      </c>
-      <c r="E42" s="10" t="s">
+      <c r="D42" s="5">
+        <v>1</v>
+      </c>
+      <c r="E42" s="5" t="s">
         <v>157</v>
       </c>
       <c r="F42" s="3" t="s">
